--- a/report_forms/031_inventory_depletion_report_log--report_forms.xlsx
+++ b/report_forms/031_inventory_depletion_report_log--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>inventory_depletion_report_log_form</t>
+          <t>inventory_depletion_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inventory_depletion_report</t>
+          <t>Inventory Depletion Date</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>stock_usage_location</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>Depleting Store Location(s)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>stock_usage_shift</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stock_usage_location</t>
+          <t>Stock Usage Shift</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>inventory_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stock_usage_location</t>
+          <t>Type of Inventory</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>inventory_depleted</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>stock_usage_location</t>
+          <t>Inventory Depleted</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>inventory_notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>stock_usage_location</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>inventory_details</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stock_usage_location</t>
+          <t>Additional Details</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inventory_depletion_date</t>
+          <t>inventory_date_range</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>stock_usage_location</t>
+          <t>Select Date Range</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>inventory_depleted_quantity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>Depleted Quantity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>inventory_reports</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>Additional Reports</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>stockroom_location</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>Stockroom Location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>inventory_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>additional_questions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>stock_usage_shift</t>
+          <t>Additional Questions</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,561 +850,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stock_usage_location_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'store_1'}</t>
+          <t>store_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Store 1'}</t>
+          <t>Store 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stock_usage_location_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'store_2'}</t>
+          <t>store_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Store 2'}</t>
+          <t>Store 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stock_usage_location_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'store_3'}</t>
+          <t>store_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Store 3'}</t>
+          <t>Store 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stock_usage_shift_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'store_1'}</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Store 1'}</t>
+          <t>Day</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stock_usage_shift_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'store_2'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Store 2'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stock_usage_shift_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'store_3'}</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Store 3'}</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>inventory_date_range_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'store_1'}</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Store 1'}</t>
+          <t>Yesterday</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>inventory_date_range_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'store_2'}</t>
+          <t>this_week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Store 2'}</t>
+          <t>This Week</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>inventory_date_range_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'store_3'}</t>
+          <t>last_week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Store 3'}</t>
+          <t>Last Week</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>inventory_reports_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'store_1'}</t>
+          <t>report_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Store 1'}</t>
+          <t>Report 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>inventory_reports_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'store_2'}</t>
+          <t>report_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Store 2'}</t>
+          <t>Report 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>inventory_reports_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'store_3'}</t>
+          <t>report_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Store 3'}</t>
+          <t>Report 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stockroom_location_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'store_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Store 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stockroom_location_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'store_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Store 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inventory_depletion_date_choices</t>
+          <t>stockroom_location_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'store_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Store 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>inventory_depletion_date_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_'store_1'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': 'Store 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>inventory_depletion_date_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'value':_'store_2'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'value': 'Store 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>inventory_depletion_date_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_'store_3'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 'Store 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'day'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'Day'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'night'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Night'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'weekend'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Weekend'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'day'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'Day'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'night'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Night'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'weekend'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'Weekend'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'day'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'Day'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'night'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'Night'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'weekend'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 'Weekend'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_'day'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': 'Day'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'night'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'Night'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_'weekend'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 'Weekend'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_'day'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 'Day'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_'night'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 'Night'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>stock_usage_shift_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_'weekend'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': 'Weekend'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
